--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HFRIG</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Det cinematiska språket: Mise-en-scène` → `BQ1088` (nedlagd 2025-03-06) — plain-text-referens; rad: - Det cinematiska språket: Mise-en-scène, 15 hp</t>
+          <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens; rad: - Konceptutveckling inom medieproduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>KFTKG</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,19 +514,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Manus för TV och film 2. Dramaturgi, genre och filmhistoria` → `BQ1050` (nedlagd 2014-05-06) — plain-text-referens; rad: - Manus för TV och film 2. Dramaturgi, genre och filmhistoria, 15 hp</t>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens; rad: - Text, kommunikation och lärande i en mångkulturell skola, 15 hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens; rad: - Konceptutveckling inom medieproduktion, 7,5 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens; rad: - Didaktik och ledarskap för ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens; rad: - Text, kommunikation och lärande i en mångkulturell skola, 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens; rad: - Didaktik och ledarskap för ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens; rad: - Didaktik och ledarskap för ämneslärare, 15 hp</t>
+          <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens; rad: - Samhällsekonomi, 7,5 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens; rad: - Didaktik och ledarskap för ämneslärare, 15 hp</t>
+          <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens; rad: - Konformitet och avvikelse, 7,5 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens; rad: - Samhällsekonomi, 7,5 hp</t>
+          <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens; rad: - Grundläggande ekonomistyrning, 7,5 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens; rad: - Konformitet och avvikelse, 7,5 hp</t>
+          <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens; rad: - Kvalitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens; rad: - Grundläggande ekonomistyrning, 7,5 hp</t>
+          <t>`Projektarbete` → `BTA009` (nedlagd 2008-05-22) — plain-text-referens; rad: - Projektarbete, 15 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -712,62 +712,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens; rad: - Kvalitativa forskningsmetoder, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>`Projektarbete` → `BTA009` (nedlagd 2008-05-22) — plain-text-referens; rad: - Projektarbete, 15 hp</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -787,10 +733,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens; rad: - Konceptutveckling inom medieproduktion, 7,5 hp</t>
+          <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens; rad: - Text, kommunikation och lärande i en mångkulturell skola, 15 hp</t>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens; rad: - Didaktik och ledarskap för ämneslärare, 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens; rad: - Didaktik och ledarskap för ämneslärare, 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens; rad: - Samhällsekonomi, 7,5 hp</t>
+          <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens; rad: - Konformitet och avvikelse, 7,5 hp</t>
+          <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens; rad: - Grundläggande ekonomistyrning, 7,5 hp</t>
+          <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens; rad: - Kvalitativa forskningsmetoder, 7,5 hp</t>
+          <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Projektarbete` → `BTA009` (nedlagd 2008-05-22) — plain-text-referens; rad: - Projektarbete, 15 hp</t>
+          <t>`Projektarbete` → `BTA009` (nedlagd 2008-05-22) — plain-text-referens</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
@@ -509,15 +531,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -536,15 +568,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2017-12-19</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -563,15 +605,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2017-12-19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -590,15 +642,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -617,15 +675,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -644,15 +708,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
@@ -671,15 +745,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
@@ -698,41 +782,51 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>`Projektarbete` → `BTA009` (nedlagd 2008-05-22) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,14 +494,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2014-03-19</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -509,19 +505,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
+          <t>`Introduktion till audiovisuell produktion` → `GLP239` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,14 +527,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -546,19 +538,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+          <t>`Audiovisuellt berättande` → `GLP23B` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -568,14 +560,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -583,19 +571,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`Audiovisuell komposition` → `GLP23A` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,14 +593,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -620,19 +604,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`Audiovisuell gestaltning` → `GLP234` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -642,7 +626,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -653,19 +637,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion` → `LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -675,7 +659,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -686,19 +670,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
+          <t>`Audiovisuella installationer` → `GLP235` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -708,14 +692,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -723,19 +703,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
+          <t>`Audiovisuell performance` → `GLP236` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -745,14 +725,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -760,54 +736,877 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
+          <t>`Kommunikationsteorier` → `GLP2MS` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>KAPSG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>`Arbetsplatsförlagd utbildning i medieproduktion` → `GLP2QD` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>KFPPG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>`Audioteknologi 1` → `GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>`Ljudteori` → `GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>`Ljudskapande till rörliga bilder` → `GLP29S` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>`Inspelning i studio` → `GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>`Audioteknologi 2` → `LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion` → `LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>`Produktionsprocesser och -villkor inom musikproduktion` → `LP1072` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>`Ljudteori` → `GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>`Inspelning i studio` → `GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>KMMPG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMMPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>KMPTG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>KMUSG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMUSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LBF3A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LP79A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2017-12-19</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LPGYA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2017-12-19</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>STMGG</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2023-03-17</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>`Projektarbete` → `BTA009` (nedlagd 2008-05-22) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -827,6 +1626,52 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -508,7 +514,12 @@
           <t>`Introduktion till audiovisuell produktion` → `GLP239` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`GLP239` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -541,7 +552,12 @@
           <t>`Audiovisuellt berättande` → `GLP23B` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`GLP23B` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -574,7 +590,12 @@
           <t>`Audiovisuell komposition` → `GLP23A` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>`GLP23A` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -607,7 +628,12 @@
           <t>`Audiovisuell gestaltning` → `GLP234` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`GLP234` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -640,7 +666,12 @@
           <t>`Vetenskaplig uppsats i Ljud- och musikproduktion` → `LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -673,7 +704,12 @@
           <t>`Audiovisuella installationer` → `GLP235` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>`GLP235` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -706,7 +742,12 @@
           <t>`Audiovisuell performance` → `GLP236` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>`GLP236` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -739,7 +780,12 @@
           <t>`Kommunikationsteorier` → `GLP2MS` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>`GLP2MS` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -772,7 +818,12 @@
           <t>`Arbetsplatsförlagd utbildning i medieproduktion` → `GLP2QD` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>`GLP2QD` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
@@ -805,7 +856,12 @@
           <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
         </is>
@@ -842,7 +898,12 @@
           <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>`BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
@@ -879,7 +940,12 @@
           <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -916,7 +982,12 @@
           <t>`Audioteknologi 1` → `GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>`GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -953,7 +1024,12 @@
           <t>`Ljudteori` → `GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -990,7 +1066,12 @@
           <t>`Ljudskapande till rörliga bilder` → `GLP29S` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>`GLP29S` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -1027,7 +1108,12 @@
           <t>`Inspelning i studio` → `GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -1064,7 +1150,12 @@
           <t>`Audioteknologi 2` → `LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>`LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -1101,7 +1192,12 @@
           <t>`Vetenskaplig uppsats i Ljud- och musikproduktion` → `LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>`LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -1138,7 +1234,12 @@
           <t>`Produktionsprocesser och -villkor inom musikproduktion` → `LP1072` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>`LP1072` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -1175,7 +1276,12 @@
           <t>`Ljudteori` → `GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1212,7 +1318,12 @@
           <t>`Inspelning i studio` → `GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1245,7 +1356,12 @@
           <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMMPG</t>
         </is>
@@ -1278,7 +1394,12 @@
           <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
         </is>
@@ -1311,7 +1432,12 @@
           <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMUSG</t>
         </is>
@@ -1348,7 +1474,12 @@
           <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>`GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1385,7 +1516,12 @@
           <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1422,7 +1558,12 @@
           <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1455,7 +1596,12 @@
           <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>`GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -1488,7 +1634,12 @@
           <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>`SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -1525,7 +1676,12 @@
           <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>`FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
@@ -1562,7 +1718,12 @@
           <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>`SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
@@ -1599,79 +1760,84 @@
           <t>`Projektarbete` → `BTA009` (nedlagd 2008-05-22) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>`BTA009` (nedlagd 2008-05-22) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G33"/>
+  <autoFilter ref="A1:H33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Introduktion till audiovisuell produktion` → `GLP239` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Introduktion till audiovisuell produktion`</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Audiovisuellt berättande` → `GLP23B` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Audiovisuellt berättande`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Audiovisuell komposition` → `GLP23A` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Audiovisuell komposition`</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Audiovisuell gestaltning` → `GLP234` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Audiovisuell gestaltning`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion` → `LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Audiovisuella installationer` → `GLP235` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Audiovisuella installationer`</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Audiovisuell performance` → `GLP236` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Audiovisuell performance`</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Kommunikationsteorier` → `GLP2MS` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Kommunikationsteorier`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning i medieproduktion` → `GLP2QD` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Arbetsplatsförlagd utbildning i medieproduktion`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion` → `BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
+          <t>`Konceptutveckling inom medieproduktion`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Audioteknologi 1` → `GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Audioteknologi 1`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Ljudteori` → `GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Ljudteori`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Ljudskapande till rörliga bilder` → `GLP29S` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Ljudskapande till rörliga bilder`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Inspelning i studio` → `GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Audioteknologi 2` → `LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Audioteknologi 2`</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion` → `LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Produktionsprocesser och -villkor inom musikproduktion` → `LP1072` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Produktionsprocesser och -villkor inom musikproduktion`</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Ljudteori` → `GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Ljudteori`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Inspelning i studio` → `GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion` → `GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola`</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`Didaktik och ledarskap för ämneslärare`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`Didaktik och ledarskap för ämneslärare`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Samhällsekonomi` → `GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`Samhällsekonomi`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Konformitet och avvikelse` → `SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
+          <t>`Konformitet och avvikelse`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Grundläggande ekonomistyrning` → `FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
+          <t>`Grundläggande ekonomistyrning`</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Kvalitativa forskningsmetoder` → `SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
+          <t>`Kvalitativa forskningsmetoder`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Projektarbete` → `BTA009` (nedlagd 2008-05-22) — plain-text-referens</t>
+          <t>`Projektarbete`</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2014-11-20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -511,17 +511,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Introduktion till audiovisuell produktion`</t>
+          <t>`Södra Afrikas moderna historia`</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>`GLP239` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`HI3013` (nedlagd 2017-10-31) — plain-text-referens</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
@@ -549,12 +549,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Audiovisuellt berättande`</t>
+          <t>`Introduktion till audiovisuell produktion`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>`GLP23B` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP239` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Audiovisuell komposition`</t>
+          <t>`Audiovisuellt berättande`</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>`GLP23A` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP23B` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Audiovisuell gestaltning`</t>
+          <t>`Audiovisuell komposition`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>`GLP234` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP23A` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+          <t>`Audiovisuell gestaltning`</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>`LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP234` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Audiovisuella installationer`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>`GLP235` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Audiovisuell performance`</t>
+          <t>`Audiovisuella installationer`</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>`GLP236` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP235` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Kommunikationsteorier`</t>
+          <t>`Audiovisuell performance`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>`GLP2MS` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP236` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning i medieproduktion`</t>
+          <t>`Kommunikationsteorier`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>`GLP2QD` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2MS` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KFPPG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -853,24 +853,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Arbetsplatsförlagd utbildning i medieproduktion`</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2QD` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>KFPPG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -880,14 +880,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2014-03-19</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -895,24 +891,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion`</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>`BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -922,14 +918,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>2021-03-23</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -937,17 +933,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Konceptutveckling inom medieproduktion`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
@@ -979,12 +975,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Audioteknologi 1`</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>`GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1021,12 +1017,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Ljudteori`</t>
+          <t>`Audioteknologi 1`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1063,12 +1059,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Ljudskapande till rörliga bilder`</t>
+          <t>`Ljudteori`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>`GLP29S` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1105,12 +1101,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Inspelning i studio`</t>
+          <t>`Ljudskapande till rörliga bilder`</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP29S` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1147,12 +1143,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Audioteknologi 2`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>`LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1189,12 +1185,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+          <t>`Audioteknologi 2`</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>`LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1231,12 +1227,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Produktionsprocesser och -villkor inom musikproduktion`</t>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>`LP1072` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1248,7 +1244,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1258,7 +1254,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1273,17 +1269,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Ljudteori`</t>
+          <t>`Produktionsprocesser och -villkor inom musikproduktion`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`LP1072` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1311,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Inspelning i studio`</t>
+          <t>`Audioteknologi I`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2JZ` (nedlagd 2026-06-25) — plain-text-referens</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1332,7 +1328,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KMMPG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1342,10 +1338,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1353,24 +1353,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Audioteknologi II`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`LP1080` (nedlagd 2026-06-25) — plain-text-referens</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KMPTG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1380,10 +1380,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1391,24 +1395,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Ljudteori`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KMUSG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1418,10 +1422,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1429,24 +1437,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Inspelning i studio`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMUSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KMMPG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1456,14 +1464,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1471,24 +1475,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola`</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>`GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMMPG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>KMPTG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1498,14 +1502,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1513,24 +1513,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare`</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>KMUSG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1540,14 +1540,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1555,24 +1551,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare`</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMUSG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1582,10 +1578,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1593,24 +1593,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Samhällsekonomi`</t>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>`GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1620,10 +1620,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>2017-12-19</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1631,24 +1635,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Konformitet och avvikelse`</t>
+          <t>`Didaktik och ledarskap för ämneslärare`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>`SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
+          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1658,12 +1662,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2017-11-15</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2023-03-17</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1673,24 +1677,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Grundläggande ekonomistyrning`</t>
+          <t>`Didaktik och ledarskap för ämneslärare`</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>`FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
+          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1700,14 +1704,10 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1715,64 +1715,186 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Kvalitativa forskningsmetoder`</t>
+          <t>`Samhällsekonomi`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>`SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
+          <t>`GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>`Konformitet och avvikelse`</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>`SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>STMGG</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2023-03-17</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>`Grundläggande ekonomistyrning`</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>`FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>`Kvalitativa forskningsmetoder`</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>`SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>`Projektarbete`</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>`BTA009` (nedlagd 2008-05-22) — plain-text-referens</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H33"/>
+  <autoFilter ref="A1:H36"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -1838,6 +1960,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>`GLP2JZ` (nedlagd 2026-06-25) — plain-text-referens</t>
+          <t>`GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>`LP1080` (nedlagd 2026-06-25) — plain-text-referens</t>
+          <t>`LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -538,10 +538,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -549,24 +553,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Introduktion till audiovisuell produktion`</t>
+          <t>`Introduktion till produktion av rörlig bild`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>`GLP239` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2UB` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,10 +580,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -587,24 +595,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Audiovisuellt berättande`</t>
+          <t>`Den korta filmens berättarstruktur`</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>`GLP23B` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2U8` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,10 +622,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -625,24 +637,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Audiovisuell komposition`</t>
+          <t>`Tillämpad filmdesign 1`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>`GLP23A` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2U7` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -652,10 +664,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -663,24 +679,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Audiovisuell gestaltning`</t>
+          <t>`Tillämpad filmdesign 2`</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>`GLP234` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2WH` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -690,10 +706,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -701,24 +721,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+          <t>`Ljudinspelning och ljudläggning inom filmdesign`</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>`LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2XD` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -728,10 +748,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -739,24 +763,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Audiovisuella installationer`</t>
+          <t>`Ljussättning och färgkorrigering inom filmdesign`</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>`GLP235` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2AZ` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -766,10 +790,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -777,24 +805,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Audiovisuell performance`</t>
+          <t>`Projektplanering och användarperspektiv`</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>`GLP236` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2NH` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -804,10 +832,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -815,24 +847,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Kommunikationsteorier`</t>
+          <t>`Informationsfilmsproduktion`</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>`GLP2MS` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2U4` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -842,10 +874,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -853,24 +889,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning i medieproduktion`</t>
+          <t>`Audiovisuell information och etik`</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>`GLP2QD` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2WG` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KFPPG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -880,10 +916,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>2018-12-20</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -891,24 +931,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Reklamfilmsproduktion`</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2WJ` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -918,12 +958,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2014-03-19</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -933,24 +973,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion`</t>
+          <t>`Vetenskapsteori och metod i Bildproduktion`</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>`BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
+          <t>`GBQ2NM` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -960,12 +1000,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -975,24 +1015,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Kvalificerad filmdesign i transmedia`</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2U5` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>HFRIG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1002,12 +1042,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2018-12-20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1017,24 +1057,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Audioteknologi 1`</t>
+          <t>`Exponeringsprojekt i Bildproduktion`</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>`GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ29E` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HFRIG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1044,14 +1084,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1059,24 +1095,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Ljudteori`</t>
+          <t>`Introduktion till audiovisuell produktion`</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP239` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1086,14 +1122,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1101,24 +1133,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Ljudskapande till rörliga bilder`</t>
+          <t>`Audiovisuellt berättande`</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>`GLP29S` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP23B` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1128,14 +1160,10 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1143,24 +1171,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Inspelning i studio`</t>
+          <t>`Audiovisuell komposition`</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP23A` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1170,14 +1198,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1185,24 +1209,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Audioteknologi 2`</t>
+          <t>`Audiovisuell gestaltning`</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>`LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP234` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1212,14 +1236,10 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1237,14 +1257,14 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1254,14 +1274,10 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1269,24 +1285,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Produktionsprocesser och -villkor inom musikproduktion`</t>
+          <t>`Audiovisuella installationer`</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>`LP1072` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP235` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1296,14 +1312,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1311,24 +1323,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Audioteknologi I`</t>
+          <t>`Audiovisuell performance`</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>`GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP236` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1338,14 +1350,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1353,24 +1361,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Audioteknologi II`</t>
+          <t>`Kommunikationsteorier`</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>`LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2MS` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1380,14 +1388,10 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2023-01-30</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1395,24 +1399,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Ljudteori`</t>
+          <t>`Arbetsplatsförlagd utbildning i medieproduktion`</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2QD` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>KFPPG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1422,14 +1426,10 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1437,24 +1437,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Inspelning i studio`</t>
+          <t>`Introduktion till medieproduktion`</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KMMPG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1464,10 +1464,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1475,24 +1479,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Manus för TV och film 1. Filmberättandets grundelement och gestaltning`</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ27K` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KMPTG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1502,10 +1506,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1513,24 +1521,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Manus för TV och film 2. Dramaturgi, manusskrivande och genre`</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`BQ1079` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KMUSG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1540,10 +1548,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1551,24 +1563,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Introduktion till medieproduktion`</t>
+          <t>`Introduktion till produktion av rörlig bild för Manus för film och TV`</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+          <t>`GBQ2HC` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMUSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1578,12 +1590,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1593,24 +1605,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola`</t>
+          <t>`Grunderna i filmproduktion för Manus för film och TV`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>`GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+          <t>`GBQ2HD` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1620,12 +1632,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1635,24 +1647,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare`</t>
+          <t>`Filmanalys och gestaltning`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`GBQ2UN` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1662,12 +1674,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1677,24 +1689,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare`</t>
+          <t>`Dokumentär metod för filmisk framställning`</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`BQ1094` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1704,10 +1716,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1715,24 +1731,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Samhällsekonomi`</t>
+          <t>`Fakta, fiktion och flerkameraproduktion`</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>`GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
+          <t>`GBQ2EB` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1742,10 +1758,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
@@ -1753,24 +1773,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Konformitet och avvikelse`</t>
+          <t>`Manus för TV och film 3. Dialog i audiovisuella medier`</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>`SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
+          <t>`GBQ2XC` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1780,12 +1800,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2017-11-15</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2023-03-17</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1795,24 +1815,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`Grundläggande ekonomistyrning`</t>
+          <t>`Manus för TV och film 4. TV-format och klassiskt berättande`</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>`FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
+          <t>`BQ2058` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1822,12 +1842,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2017-11-15</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2023-03-17</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1837,64 +1857,1582 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`Kvalitativa forskningsmetoder`</t>
+          <t>`Vetenskapsteori och metod i Bildproduktion`</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>`SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
+          <t>`GBQ2NM` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>KFTKG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>`Kvalificerat filmmanusprojekt`</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>`GBQ2QB` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>`Introduktion till produktion av rörlig bild`</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>`GBQ2UB` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>`Grunderna i filmproduktion`</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>`GBQ3A5` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>`TV-nyheter och flerkameraproduktion`</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>`BQ1081` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>`Flerkameraproduktion, fördjupning`</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>`GBQ29D` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>`Kvalificerad filmproduktion`</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>`GBQ22U` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori och metod i Bildproduktion`</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>`GBQ2NM` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>`Konceptutveckling inom medieproduktion`</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>`BQ2049` (nedlagd 2025-03-06) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>KFTPG</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>`Exponeringsprojekt i bildproduktion`</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>`GBQ29E` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion`</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>`Audioteknologi 1`</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>`GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>`Ljudteori`</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>`Ljudskapande till rörliga bilder`</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>`GLP29S` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>`Inspelning i studio`</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>`Audioteknologi 2`</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>`LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>`Vetenskaplig uppsats i Ljud- och musikproduktion`</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>`LP1065` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>KLJMG</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>`Produktionsprocesser och -villkor inom musikproduktion`</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>`LP1072` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>`Audioteknologi I`</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>`GLP29R` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>`Audioteknologi II`</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>`LP1080` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>`Ljudteori`</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>`GLP2FP` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>`Inspelning i studio`</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>`GLP2QU` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>KMMPG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion`</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMMPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>KMPTG</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion`</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>KMUSG</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>`Introduktion till medieproduktion`</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>`GLP2FH` (nedlagd 2026-06-25) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMUSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>LBF3A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola`</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>`GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>LP79A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2017-12-19</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap för ämneslärare`</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>LPGYA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2017-12-19</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap för ämneslärare`</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SBMPG</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>`Organisation B`</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>`FÖ1042` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SDUVA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2012-05-02</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>`Marknadsföring av platser och destinationer`</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>`FÖ3035` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SENGR</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>`Organisation B`</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>`FÖ1042` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>SMHTA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>`Marknadsföring av platser och destinationer`</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>`FÖ3035` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SPTMG</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>`Organisation B`</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>`FÖ1042` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPTMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>`Samhällsekonomi`</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>`GSQ25R` (nedlagd 2025-12-08) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>`Konformitet och avvikelse`</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>`SO1007` (nedlagd 2025-11-13) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
           <t>STMGG</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
         <is>
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>2023-03-17</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Programmet listar nedlagd kurs</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>`Grundläggande ekonomistyrning`</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>`FEA034` (nedlagd 2008-03-18) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>`Turismmarknadsföring`</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>`GFÖ35J` (nedlagd 2026-09-01) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>`Kvalitativa forskningsmetoder`</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>`SB3002` (nedlagd 2013-01-15) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>`Projektarbete`</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>`BTA009` (nedlagd 2008-05-22) — plain-text-referens</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H36"/>
+  <autoFilter ref="A1:H73"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -1966,6 +3504,80 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
